--- a/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_classification_report.xlsx
+++ b/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_classification_report.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="C2" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="D2" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -476,16 +476,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="C3" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="D3" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -495,13 +495,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -531,10 +531,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="E6" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="C7" t="n">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="D7" t="n">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="E7" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -563,16 +563,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="C8" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="D8" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="E8" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -585,7 +585,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Note: Overall Accuracy = 0.8182; Number of sites = 33.0</t>
+          <t>Note: Overall Accuracy = 0.8621; Number of sites = 29.0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
